--- a/assets/docs/lop2/Hoat dong trai nghiem - Lop 2.xlsx
+++ b/assets/docs/lop2/Hoat dong trai nghiem - Lop 2.xlsx
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Khám phá bản thân</t>
+          <t>Chủ đề: Rèn nếp sống</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Khám phá bản thân</t>
+          <t>Chủ đề: Rèn nếp sống</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr"/>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Khám phá bản thân</t>
+          <t>Chủ đề: Rèn nếp sống</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr"/>
@@ -1133,7 +1133,8 @@
       <c r="H21" s="4" t="inlineStr">
         <is>
           <t>Năng lực số 1.3 CB1a: Nhận biết được nơi để sắp xếp dữ liệu, thông tin một cách đơn giản trong môi trường có cấu trúc.
-Tích hợp AI - YCCĐ 2.A2.1: Nhận biết các thiết bị thông minh (AI) hỗ trợ việc học tập tiện nghi hơn.</t>
+Tích hợp AI - YCCĐ 2.A2.1: Nhận biết các thiết bị thông minh (AI) hỗ trợ việc học tập tiện nghi hơn.
+KNS: KN tự đánh giá và đánh giá bạn một cách khách quan, thiện chí.</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1146,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 20/10</t>
+          <t>Chủ đề: Rèn nếp sống</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr"/>
@@ -1179,7 +1180,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 20/10</t>
+          <t>Chủ đề: Rèn nếp sống</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr"/>
@@ -1213,7 +1214,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 20/10</t>
+          <t>Chủ đề: Rèn nếp sống</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr"/>
@@ -1249,7 +1250,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 20/10</t>
+          <t>Chủ đề: Rèn nếp sống</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr"/>
@@ -1284,7 +1285,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 20/10</t>
+          <t>Chủ đề: Rèn nếp sống</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr"/>
@@ -1319,7 +1320,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 20/10</t>
+          <t>Chủ đề: Rèn nếp sống</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr"/>
@@ -1355,7 +1356,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 20/10</t>
+          <t>Chủ đề: Em yêu trường em</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr"/>
@@ -1385,7 +1386,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 20/10</t>
+          <t>Chủ đề: Em yêu trường em</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr"/>
@@ -1419,7 +1420,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 20/10</t>
+          <t>Chủ đề: Em yêu trường em</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr"/>
@@ -1455,7 +1456,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 20/10</t>
+          <t>Chủ đề: Em yêu trường em</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr"/>
@@ -1489,7 +1490,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 20/10</t>
+          <t>Chủ đề: Em yêu trường em</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr"/>
@@ -1523,7 +1524,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 20/10</t>
+          <t>Chủ đề: Em yêu trường em</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr"/>
@@ -1559,7 +1560,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 20/10</t>
+          <t>Chủ đề: Em yêu trường em</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr"/>
@@ -1593,7 +1594,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 20/10</t>
+          <t>Chủ đề: Em yêu trường em</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
@@ -1627,7 +1628,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 20/10</t>
+          <t>Chủ đề: Em yêu trường em</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr"/>
@@ -1662,7 +1663,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 20/11</t>
+          <t>Chủ đề: Em yêu trường em</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr"/>
@@ -1692,7 +1693,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 20/11</t>
+          <t>Chủ đề: Em yêu trường em</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr"/>
@@ -1727,7 +1728,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 20/11</t>
+          <t>Chủ đề: Em yêu trường em</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr"/>
@@ -1762,7 +1763,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 20/11</t>
+          <t>Chủ đề: Tự phục vụ bản thân</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr"/>
@@ -1796,7 +1797,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 20/11</t>
+          <t>Chủ đề: Tự phục vụ bản thân</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr"/>
@@ -1819,7 +1820,8 @@
       <c r="H41" s="4" t="inlineStr">
         <is>
           <t>Tích hợp AI - YCCĐ 2.A2.1: Biết mục đích của AI là hỗ trợ tiết kiệm thời gian; con người vẫn cần tự lập trong các việc cá nhân để trưởng thành.
-Năng lực số 5.2 CB1b: HS chọn được cách ứng phó đúng trong từng tình huống và đọc thuộc các số gọi khẩn cấp.</t>
+Năng lực số 5.2 CB1b: HS chọn được cách ứng phó đúng trong từng tình huống và đọc thuộc các số gọi khẩn cấp.
+KNS: KN tự nhận thức: nhận ra điểm mạnh, điểm cần cố gắng của bản thân.</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1833,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 20/11</t>
+          <t>Chủ đề: Tự phục vụ bản thân</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr"/>
@@ -1853,8 +1855,7 @@
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB1b: HS chọn được cách ứng phó an toàn trong trò đố vui và giải thích được vì sao.
-KNS: KN tự đánh giá và đánh giá bạn một cách khách quan, thiện chí.</t>
+          <t>Năng lực số 5.2 CB1b: HS chọn được cách ứng phó an toàn trong trò đố vui và giải thích được vì sao.</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1867,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 20/11</t>
+          <t>Chủ đề: Tự phục vụ bản thân</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr"/>
@@ -1888,8 +1889,7 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 3.1 CB1b: HS chọn cách giới thiệu sản phẩm/hình ảnh theo chủ điểm bằng phương tiện số đơn giản.
-KNS: KN lao động tự phục vụ và bước đầu tìm hiểu nghề nghiệp.</t>
+          <t>Năng lực số 3.1 CB1b: HS chọn cách giới thiệu sản phẩm/hình ảnh theo chủ điểm bằng phương tiện số đơn giản.</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 20/11</t>
+          <t>Chủ đề: Tự phục vụ bản thân</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr"/>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 20/11</t>
+          <t>Chủ đề: Tự phục vụ bản thân</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr"/>
@@ -1958,8 +1958,7 @@
       <c r="H45" s="4" t="inlineStr">
         <is>
           <t>Tích hợp AI - YCCĐ 2.D1.1: HS nêu được một số vấn đề gần gũi có thể áp dụng AI để hỗ trợ giải quyết; hiểu AI chỉ nhắc nhở, con người vẫn quyết định và chịu trách nhiệm.
-Năng lực số 5.2 CB1b: HS chọn được cách ứng phó an toàn trong trò đố vui và giải thích được vì sao.
-KNS: KN tự đánh giá và đánh giá bạn một cách khách quan, thiện chí.</t>
+Năng lực số 5.2 CB1b: HS chọn được cách ứng phó an toàn trong trò đố vui và giải thích được vì sao.</t>
         </is>
       </c>
     </row>
@@ -1971,7 +1970,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 20/11</t>
+          <t>Chủ đề: Tự phục vụ bản thân</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr"/>
@@ -2001,7 +2000,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 20/11</t>
+          <t>Chủ đề: Tự phục vụ bản thân</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr"/>
@@ -2023,7 +2022,8 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB1a: Nhận biết công cụ số đơn giản như đồng hồ báo thức, lịch hoặc ứng dụng nhắc việc có thể hỗ trợ tự giác học tập, sinh hoạt dưới sự hướng dẫn của người lớn.</t>
+          <t>Tích hợp AI - YCCĐ 2.C3.1: HS biết AI hỗ trợ phân loại, gợi ý trang phục dựa trên dữ liệu; con người phải kiểm tra và quyết định.
+Năng lực số 1.1 CB1b: HS đọc bản tin thời tiết chiếu trên màn hình và chọn được trang phục, đồ dùng hợp với thời tiết những ngày tới.</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 20/11</t>
+          <t>Chủ đề: Tự phục vụ bản thân</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr"/>
@@ -2057,8 +2057,7 @@
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB1b: HS chọn được cách ứng phó an toàn trong trò đố vui và giải thích được vì sao.
-KNS: KN tự đánh giá và đánh giá bạn một cách khách quan, thiện chí.</t>
+          <t>Năng lực số 5.2 CB1b: HS chọn được cách ứng phó an toàn trong trò đố vui và giải thích được vì sao.</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2069,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 22/12</t>
+          <t>Chủ đề: Tự phục vụ bản thân</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr"/>
@@ -2092,8 +2091,7 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 3.1 CB1b: HS chọn cách giới thiệu sản phẩm/hình ảnh theo chủ điểm bằng phương tiện số đơn giản.
-QPAN: Tổ chức hoạt động tìm hiểu, thăm hỏi, tri ân gia đình thương binh, liệt sĩ, đơn vị bộ đội, công an trên địa bàn; giới thiệu tinh thần đoàn kết toàn dân tộc và sự hi sinh của các chiến sĩ cách mạng.</t>
+          <t>QPAN: Tổ chức hoạt động tìm hiểu, thăm hỏi, tri ân gia đình thương binh, liệt sĩ, đơn vị bộ đội, công an trên địa bàn; giới thiệu tinh thần đoàn kết toàn dân tộc và sự hi sinh của các chiến sĩ cách mạng.</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2103,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 22/12</t>
+          <t>Chủ đề: Tự phục vụ bản thân</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr"/>
@@ -2127,8 +2125,7 @@
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>Tích hợp AI - YCCĐ 2.C3.1: HS biết AI hỗ trợ phân loại, gợi ý trang phục dựa trên dữ liệu; con người phải kiểm tra và quyết định.
-Năng lực số 1.1 CB1b: HS đọc bản tin thời tiết chiếu trên màn hình và chọn được trang phục, đồ dùng hợp với thời tiết những ngày tới.</t>
+          <t>Năng lực số 5.2 CB1a: Nhận biết công cụ số đơn giản như đồng hồ báo thức, lịch hoặc ứng dụng nhắc việc có thể hỗ trợ tự giác học tập, sinh hoạt dưới sự hướng dẫn của người lớn.</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2137,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 22/12</t>
+          <t>Chủ đề: Tự phục vụ bản thân</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr"/>
@@ -2162,8 +2159,7 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 3.1 CB1a: HS xem bộ ảnh trình diễn và nói được trang phục nào hợp với hoàn cảnh nào.
-KNS: KN tự đánh giá và đánh giá bạn một cách khách quan, thiện chí.</t>
+          <t>Năng lực số 3.1 CB1a: HS xem bộ ảnh trình diễn và nói được trang phục nào hợp với hoàn cảnh nào.</t>
         </is>
       </c>
     </row>
@@ -2175,7 +2171,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 22/12</t>
+          <t>Chủ đề: Tự phục vụ bản thân</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr"/>
@@ -2195,11 +2191,7 @@
           <t>49</t>
         </is>
       </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>KNS: KN lao động tự phục vụ và bước đầu tìm hiểu nghề nghiệp.</t>
-        </is>
-      </c>
+      <c r="H52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -2209,7 +2201,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 22/12</t>
+          <t>Chủ đề: Tự phục vụ bản thân</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr"/>
@@ -2243,7 +2235,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 22/12</t>
+          <t>Chủ đề: Tự phục vụ bản thân</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr"/>
@@ -2265,8 +2257,7 @@
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 3.1 CB1a: HS xem bộ ảnh trình diễn và nói được trang phục nào hợp với hoàn cảnh nào.
-KNS: KN tự đánh giá và đánh giá bạn một cách khách quan, thiện chí.</t>
+          <t>Năng lực số 3.1 CB1a: HS xem bộ ảnh trình diễn và nói được trang phục nào hợp với hoàn cảnh nào.</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2373,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Trước Tết</t>
+          <t>Chủ đề: Gia đình thân thương</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr"/>
@@ -2416,7 +2407,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Trước Tết</t>
+          <t>Chủ đề: Gia đình thân thương</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr"/>
@@ -2450,7 +2441,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Trước Tết</t>
+          <t>Chủ đề: Gia đình thân thương</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr"/>
@@ -2485,7 +2476,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Trước Tết</t>
+          <t>Chủ đề: Gia đình thân thương</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr"/>
@@ -2519,7 +2510,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Trước Tết</t>
+          <t>Chủ đề: Gia đình thân thương</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr"/>
@@ -2554,7 +2545,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Trước Tết</t>
+          <t>Chủ đề: Gia đình thân thương</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr"/>
@@ -2589,7 +2580,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Trước Tết</t>
+          <t>Chủ đề: Tự chăm sóc và bảo vệ bản thân</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr"/>
@@ -2609,7 +2600,11 @@
           <t>61</t>
         </is>
       </c>
-      <c r="H64" s="4" t="inlineStr"/>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>KNS: KN tự nhận thức: nhận ra điểm mạnh, điểm cần cố gắng của bản thân.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -2619,7 +2614,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Trước Tết</t>
+          <t>Chủ đề: Tự chăm sóc và bảo vệ bản thân</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr"/>
@@ -2654,7 +2649,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Trước Tết</t>
+          <t>Chủ đề: Tự chăm sóc và bảo vệ bản thân</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr"/>
@@ -2689,7 +2684,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Trước Tết</t>
+          <t>Chủ đề: Tự chăm sóc và bảo vệ bản thân</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr"/>
@@ -2709,11 +2704,7 @@
           <t>64</t>
         </is>
       </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>KNS: KN ứng phó với tình huống nguy hiểm và tìm kiếm sự trợ giúp.</t>
-        </is>
-      </c>
+      <c r="H67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
@@ -2723,7 +2714,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Trước Tết</t>
+          <t>Chủ đề: Tự chăm sóc và bảo vệ bản thân</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr"/>
@@ -2758,7 +2749,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Trước Tết</t>
+          <t>Chủ đề: Tự chăm sóc và bảo vệ bản thân</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr"/>
@@ -2780,8 +2771,7 @@
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB1b: HS trả lời đúng câu hỏi trong trò chơi và nêu được việc giữ vệ sinh có tác dụng gì.
-KNS: KN tự đánh giá và đánh giá bạn một cách khách quan, thiện chí.</t>
+          <t>Năng lực số 5.2 CB1b: HS trả lời đúng câu hỏi trong trò chơi và nêu được việc giữ vệ sinh có tác dụng gì.</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2783,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Trước Tết</t>
+          <t>Chủ đề: Tự chăm sóc và bảo vệ bản thân</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr"/>
@@ -2815,8 +2805,7 @@
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>QTE: QTE: trẻ em có quyền được bảo vệ khỏi mọi hình thức xâm hại; nhớ số của người thân và Tổng đài quốc gia bảo vệ trẻ em 111.
-KNS: KN ứng phó với tình huống nguy hiểm và tìm kiếm sự trợ giúp.</t>
+          <t>QTE: QTE: trẻ em có quyền được bảo vệ khỏi mọi hình thức xâm hại; nhớ số của người thân và Tổng đài quốc gia bảo vệ trẻ em 111.</t>
         </is>
       </c>
     </row>
@@ -2828,7 +2817,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Trước Tết</t>
+          <t>Chủ đề: Tự chăm sóc và bảo vệ bản thân</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr"/>
@@ -2850,113 +2839,109 @@
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
+          <t>Năng lực số 4.2 CB1a: Nhận biết cách sử dụng và chia sẻ thông tin định danh cá nhân an toàn; không chia sẻ địa chỉ nhà, số điện thoại hoặc thông tin cá nhân cho người lạ trên môi trường số.
+QTE: QTE: trẻ em có quyền được bảo vệ khỏi mọi hình thức xâm hại; nhớ số của người thân và Tổng đài quốc gia bảo vệ trẻ em 111.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>Chủ đề: Tự chăm sóc và bảo vệ bản thân</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr"/>
+      <c r="D72" s="4" t="inlineStr"/>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>Sinh hoạt lớp: Phòng tránh bị bắt cóc</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 5.2 CB1b: HS đóng vai và xem lại đoạn phim của nhóm mình, chỉ ra được chỗ mình còn lưỡng lự.
+QTE: QTE: trẻ em có quyền được bảo vệ khỏi mọi hình thức xâm hại; nhớ số của người thân và Tổng đài quốc gia bảo vệ trẻ em 111.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Chủ đề: Tự chăm sóc và bảo vệ bản thân</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr"/>
+      <c r="D73" s="4" t="inlineStr"/>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>Sinh hoạt dưới cờ: Văn nghệ chào mừng ngày Quốc tế Phụ nữ 8-3; xem tiểu phẩm "Chú vịt xám lạc mẹ"</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>Chủ đề: Tự chăm sóc và bảo vệ bản thân</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr"/>
+      <c r="D74" s="4" t="inlineStr"/>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>Hoạt động giáo dục theo chủ đề: Câu chuyện lạc đường</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
           <t>Năng lực số 5.2 CB1a: Sử dụng công cụ số đơn giản để giải quyết nhu cầu cá nhân dưới sự hướng dẫn; biết điện thoại thông minh, bản đồ hoặc định vị có thể hỗ trợ tìm đường, gửi vị trí cho người thân khi gặp sự cố.
 Năng lực số 4.2 CB1a: Nhận biết cách bảo vệ thông tin định danh cá nhân; biết địa chỉ nhà, số điện thoại của bố mẹ và thông tin liên lạc khẩn cấp chỉ dùng để nhờ người tin cậy hỗ trợ, không đăng công khai lên mạng.
 Tích hợp AI - YCCĐ 2.A1.1: Biết sử dụng công cụ tìm kiếm hoặc bản đồ AI để tìm trợ giúp khi cần.
-QTE: QTE: trẻ em có quyền được bảo vệ khỏi mọi hình thức xâm hại; nhớ số của người thân và Tổng đài quốc gia bảo vệ trẻ em 111.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>Chủ đề: Trước Tết</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="inlineStr"/>
-      <c r="D72" s="4" t="inlineStr"/>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>Sinh hoạt lớp: Phòng tránh bị bắt cóc</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G72" s="4" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB1b: HS đóng vai và xem lại đoạn phim của nhóm mình, chỉ ra được chỗ mình còn lưỡng lự.
-QTE: QTE: trẻ em có quyền được bảo vệ khỏi mọi hình thức xâm hại; nhớ số của người thân và Tổng đài quốc gia bảo vệ trẻ em 111.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>Chủ đề: 8/3</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr"/>
-      <c r="D73" s="4" t="inlineStr"/>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>Sinh hoạt dưới cờ: Văn nghệ chào mừng ngày Quốc tế Phụ nữ 8-3; xem tiểu phẩm "Chú vịt xám lạc mẹ"</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G73" s="4" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="H73" s="4" t="inlineStr">
-        <is>
-          <t>KNS: KN lao động tự phục vụ và bước đầu tìm hiểu nghề nghiệp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t>Chủ đề: 8/3</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="inlineStr"/>
-      <c r="D74" s="4" t="inlineStr"/>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>Hoạt động giáo dục theo chủ đề: Câu chuyện lạc đường</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G74" s="4" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 4.2 CB1a: Nhận biết cách sử dụng và chia sẻ thông tin định danh cá nhân an toàn; không chia sẻ địa chỉ nhà, số điện thoại hoặc thông tin cá nhân cho người lạ trên môi trường số.
 ATGT: ATGT: đi thành hàng, bám sát người phụ trách khi ra khỏi trường; đội mũ bảo hiểm cài quai khi ngồi sau xe máy, xe đạp điện.</t>
         </is>
       </c>
@@ -2969,7 +2954,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 8/3</t>
+          <t>Chủ đề: Tự chăm sóc và bảo vệ bản thân</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr"/>
@@ -3004,7 +2989,7 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 8/3</t>
+          <t>Chủ đề: Chia sẻ cộng đồng</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr"/>
@@ -3026,7 +3011,8 @@
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN ứng phó với tình huống nguy hiểm và tìm kiếm sự trợ giúp.</t>
+          <t>QPAN: Tổ chức tham quan di tích lịch sử, nhà truyền thống ở địa phương hoặc xem tư liệu thay thế; giáo dục biết ơn người có công với cách mạng; kính trọng cán bộ, chiến sĩ đang làm nhiệm vụ bảo vệ Tổ quốc.
+KNS: KN giao tiếp – hợp tác: làm việc nhóm, chia sẻ và giải quyết bất đồng ôn hoà.</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3024,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 8/3</t>
+          <t>Chủ đề: Chia sẻ cộng đồng</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr"/>
@@ -3072,7 +3058,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 8/3</t>
+          <t>Chủ đề: Chia sẻ cộng đồng</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr"/>
@@ -3094,8 +3080,7 @@
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS nghe sách nói và nói được cảm nhận của mình khi chỉ nghe mà không nhìn chữ.
-KNS: KN tự đánh giá và đánh giá bạn một cách khách quan, thiện chí.</t>
+          <t>Năng lực số 1.1 CB1b: HS nghe sách nói và nói được cảm nhận của mình khi chỉ nghe mà không nhìn chữ.</t>
         </is>
       </c>
     </row>
@@ -3107,7 +3092,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 8/3</t>
+          <t>Chủ đề: Chia sẻ cộng đồng</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr"/>
@@ -3141,7 +3126,7 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 8/3</t>
+          <t>Chủ đề: Chia sẻ cộng đồng</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr"/>
@@ -3175,7 +3160,7 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 8/3</t>
+          <t>Chủ đề: Chia sẻ cộng đồng</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr"/>
@@ -3197,8 +3182,7 @@
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS nghe sách nói và nói được cảm nhận của mình khi chỉ nghe mà không nhìn chữ.
-KNS: KN tự đánh giá và đánh giá bạn một cách khách quan, thiện chí.</t>
+          <t>Năng lực số 1.1 CB1b: HS nghe sách nói và nói được cảm nhận của mình khi chỉ nghe mà không nhìn chữ.</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3194,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 8/3</t>
+          <t>Chủ đề: Chia sẻ cộng đồng</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr"/>
@@ -3240,7 +3224,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 8/3</t>
+          <t>Chủ đề: Chia sẻ cộng đồng</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr"/>
@@ -3276,7 +3260,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 8/3</t>
+          <t>Chủ đề: Chia sẻ cộng đồng</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr"/>
@@ -3577,7 +3561,7 @@
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB1a: Xác định nhu cầu cá nhân và sử dụng công cụ số đơn giản để trình bày kết quả; dưới sự hướng dẫn của GV, HS biết dùng bảng hoặc biểu tượng số đơn giản để trình bày kết quả khảo sát khu vực sạch - chưa sạch.</t>
+          <t>Năng lực số 4.4 CB1a: Nhận biết tác động của công nghệ số đối với môi trường; biết thu gom pin cũ, thiết bị điện tử hỏng đúng nơi quy định.</t>
         </is>
       </c>
     </row>
@@ -3611,8 +3595,7 @@
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>Tích hợp AI - YCCĐ 2.C3.1: HS biết AI có thể hỗ trợ phân loại rác thải tự động để bảo vệ môi trường.
-Năng lực số 3.1 CB1a: HS chụp ảnh và báo số liệu cho GV ghi vào sổ chăm sóc cây của tổ mình.
+          <t>Năng lực số 3.1 CB1a: HS chụp ảnh và báo số liệu cho GV ghi vào sổ chăm sóc cây của tổ mình.
 KNS: KN tự đánh giá và đánh giá bạn một cách khách quan, thiện chí.</t>
         </is>
       </c>
@@ -3625,7 +3608,7 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Môi trường quanh em</t>
+          <t>Chủ đề: Em tìm hiểu nghề nghiệp</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr"/>
@@ -3660,7 +3643,7 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Môi trường quanh em</t>
+          <t>Chủ đề: Em tìm hiểu nghề nghiệp</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr"/>
@@ -3682,7 +3665,8 @@
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 4.4 CB1a: Nhận biết tác động của công nghệ số đối với môi trường; biết thu gom pin cũ, thiết bị điện tử hỏng đúng nơi quy định.
+          <t>Tích hợp AI – YCCĐ 2.A1.2: Nhận biết trong nghề nghiệp thực tế, AI có thể hỗ trợ nhưng con người phải giám sát và chịu trách nhiệm.
+Năng lực số 1.1 CB1b: HS xem phim, gọi tên được một số nghề và nêu đức tính cần có của người làm nghề đó.
 KNS: KN lao động tự phục vụ và bước đầu tìm hiểu nghề nghiệp.</t>
         </is>
       </c>
@@ -3695,7 +3679,7 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Môi trường quanh em</t>
+          <t>Chủ đề: Em tìm hiểu nghề nghiệp</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr"/>
@@ -3717,7 +3701,7 @@
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 3.1 CB1a: HS chụp ảnh và báo số liệu cho GV ghi vào sổ chăm sóc cây của tổ mình.
+          <t>Năng lực số 5.2 CB1b: HS đoán đúng tên nghề qua câu đố và tiếng động trong trò chơi.
 KNS: KN lao động tự phục vụ và bước đầu tìm hiểu nghề nghiệp.</t>
         </is>
       </c>
@@ -3730,7 +3714,7 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Môi trường quanh em</t>
+          <t>Chủ đề: Em tìm hiểu nghề nghiệp</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr"/>
@@ -3765,7 +3749,7 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Môi trường quanh em</t>
+          <t>Chủ đề: Em tìm hiểu nghề nghiệp</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr"/>
@@ -3801,7 +3785,7 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Môi trường quanh em</t>
+          <t>Chủ đề: Em tìm hiểu nghề nghiệp</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr"/>
@@ -3836,7 +3820,7 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Môi trường quanh em</t>
+          <t>Chủ đề: Em tìm hiểu nghề nghiệp</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr"/>
@@ -3858,8 +3842,8 @@
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS tìm thông tin đơn giản về nghề nghiệp từ nguồn số phù hợp.
-QPAN: Tổ chức tham quan di tích lịch sử, nhà truyền thống ở địa phương hoặc xem tư liệu thay thế; giáo dục biết ơn người có công với cách mạng; kính trọng cán bộ, chiến sĩ đang làm nhiệm vụ bảo vệ Tổ quốc.</t>
+          <t>QPAN: Tổ chức tham quan di tích lịch sử, nhà truyền thống ở địa phương hoặc xem tư liệu thay thế; giáo dục biết ơn người có công với cách mạng; kính trọng cán bộ, chiến sĩ đang làm nhiệm vụ bảo vệ Tổ quốc.
+KNS: KN lao động tự phục vụ và bước đầu tìm hiểu nghề nghiệp.</t>
         </is>
       </c>
     </row>
@@ -3871,7 +3855,7 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Môi trường quanh em</t>
+          <t>Chủ đề: Em tìm hiểu nghề nghiệp</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr"/>
@@ -3893,7 +3877,7 @@
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS xem phim, gọi tên được một số nghề và nêu đức tính cần có của người làm nghề đó.
+          <t>Năng lực số 5.2 CB1a: Xác định nhu cầu cá nhân và sử dụng công cụ số đơn giản để trình bày kết quả; dưới sự hướng dẫn của GV, HS biết dùng bảng hoặc biểu tượng số đơn giản để trình bày kết quả khảo sát khu vực sạch - chưa sạch.
 QPAN: Tổ chức tham quan di tích lịch sử, nhà truyền thống ở địa phương hoặc xem tư liệu thay thế; giáo dục biết ơn người có công với cách mạng; kính trọng cán bộ, chiến sĩ đang làm nhiệm vụ bảo vệ Tổ quốc.</t>
         </is>
       </c>
@@ -3906,7 +3890,7 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Môi trường quanh em</t>
+          <t>Chủ đề: Em tìm hiểu nghề nghiệp</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr"/>
@@ -3941,7 +3925,7 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 19/5</t>
+          <t>Chủ đề: Em tìm hiểu nghề nghiệp</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr"/>
@@ -3976,7 +3960,7 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 19/5</t>
+          <t>Chủ đề: Em tìm hiểu nghề nghiệp</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr"/>
@@ -4011,7 +3995,7 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 19/5</t>
+          <t>Chủ đề: Em tìm hiểu nghề nghiệp</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr"/>
@@ -4047,7 +4031,7 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 19/5</t>
+          <t>Chủ đề: Hoạt động tổng kết năm học</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr"/>
@@ -4067,7 +4051,11 @@
           <t>103</t>
         </is>
       </c>
-      <c r="H106" s="4" t="inlineStr"/>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>KNS: KN tự đánh giá và đánh giá bạn một cách khách quan, thiện chí.</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -4077,14 +4065,14 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 19/5</t>
+          <t>Chủ đề: Hoạt động tổng kết năm học</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr"/>
       <c r="D107" s="4" t="inlineStr"/>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hoạt động giáo dục theo chủ đề: </t>
+          <t>Hoạt động giáo dục theo chủ đề: Đón mùa hè trải nghiệm</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
@@ -4111,7 +4099,7 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: 19/5</t>
+          <t>Chủ đề: Hoạt động tổng kết năm học</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr"/>
